--- a/data/trans_dic/IP11D_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han sufrido algún tipo de agresión</t>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,52</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,85</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,3</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,04</t>
+          <t>0,44; 4,35</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 9,86</t>
+          <t>0,79; 10,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,98</t>
+          <t>0,36; 4,75</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,92</t>
+          <t>0,91; 5,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,4</t>
+          <t>0,73; 3,63</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,01</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,63</t>
+          <t>0,32; 1,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,36</t>
+          <t>0,63; 2,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,7</t>
+          <t>0,64; 1,72</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún tipo de agresión (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3082</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4717</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5213</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1765</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5017</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5475</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>836; 8269</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1874</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1875</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>412; 5376</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>421; 5498</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5440</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6917</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5293</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1982; 12838</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3175; 15842</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5920</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 6323</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5394</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>9687</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15080</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2120; 9854</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4682; 18081</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>9026; 24115</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11D_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,05</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,95</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,45</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 7,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,35</t>
+          <t>0,47; 3,87</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 10,37</t>
+          <t>0,83; 10,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,75</t>
+          <t>0,36; 4,86</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,88</t>
+          <t>0,98; 6,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,63</t>
+          <t>0,66; 3,32</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,5</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,42</t>
+          <t>0,66; 2,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,72</t>
+          <t>0,67; 1,77</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3082</t>
+          <t>0; 3184</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4717</t>
+          <t>0; 4035</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5213</t>
+          <t>0; 4609</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5017</t>
+          <t>0; 5382</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5475</t>
+          <t>0; 7226</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>836; 8269</t>
+          <t>890; 7345</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>412; 5376</t>
+          <t>432; 5468</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>421; 5498</t>
+          <t>417; 5623</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5293</t>
+          <t>0; 5066</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1982; 12838</t>
+          <t>2145; 13325</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3175; 15842</t>
+          <t>2869; 14471</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5920</t>
+          <t>0; 7069</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6323</t>
+          <t>0; 6608</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2120; 9854</t>
+          <t>2399; 9953</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4682; 18081</t>
+          <t>4955; 18384</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9026; 24115</t>
+          <t>9419; 24898</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11D_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11D_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,71</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,56</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,87</t>
+          <t>0,45; 4,2</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 10,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,84; 9,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,86</t>
+          <t>0,4; 5,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,97; 6,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 6,1</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,32</t>
+          <t>0,71; 3,55</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,37</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,51</t>
+          <t>0,63; 2,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,46</t>
+          <t>0,43; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,77</t>
+          <t>0,66; 1,72</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>641</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>655</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1297</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3184</t>
+          <t>0; 3627</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4035</t>
+          <t>0; 2730</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4609</t>
+          <t>0; 4415</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3239</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5382</t>
+          <t>0; 6983</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7226</t>
+          <t>0; 4627</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>890; 7345</t>
+          <t>852; 7870</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1910</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>432; 5468</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>448; 5230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>417; 5623</t>
+          <t>442; 5727</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6262</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5066</t>
+          <t>1949; 13328</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2145; 13325</t>
+          <t>0; 4497</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2869; 14471</t>
+          <t>2688; 13523</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1381</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0; 5465</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0; 7069</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6608</t>
+          <t>0; 5097</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14089</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2399; 9953</t>
+          <t>4306; 15787</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4955; 18384</t>
+          <t>2661; 10987</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9419; 24898</t>
+          <t>8585; 22466</t>
         </is>
       </c>
     </row>
